--- a/invalidCodes/invalidCodes_InventarioCEA.xlsx.xlsx
+++ b/invalidCodes/invalidCodes_InventarioCEA.xlsx.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L339"/>
+  <dimension ref="A1:L229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Códgo</t>
+          <t>CMD09-2</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>CONEC. CODO 3/8 SERIE (BX 10)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -466,13 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Un.</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Cantidad</t>
-        </is>
+          <t>PZA</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
@@ -493,13 +491,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>50AT10BN25DDN</t>
+          <t>24-210-6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FILTRO DE 10MICRAS, 30GPM, LOW PRESS, PUERTOS 1 ¼” MODELO 50AT10BN25DDN</t>
+          <t>IPS TORNILLO CABEZA PLANA M6 X 10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -512,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -521,13 +519,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>216P-4</t>
+          <t>24-225-5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIPLE 1/4 NPT MACHO-MACHO</t>
+          <t>IPS M5x25 FLAT HEAD SCREW No PARTE 24-225-5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -549,13 +547,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>800FP-P4</t>
+          <t>EZ11NBB553A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OPERADOR PARA LUZ PILOTO PLASTICO COLOR ROJO</t>
+          <t>VALVULA NEUMATICA EZ11NBB553A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -577,13 +575,13 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>800F-X01</t>
+          <t>FDR12H000000-02000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CONTACTO NC</t>
+          <t>GUIA ORIGA DE 12MM X 2000MM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -592,7 +590,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>MTS.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -605,13 +603,13 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>802T-W1A</t>
+          <t>H21WXBG2B9000FC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LEVA DE INTERRUPTOR</t>
+          <t>VALVULA PARKER MODELO H21WXBG2B900FC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -624,7 +622,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -633,13 +631,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XTMCXFA13</t>
+          <t>K022112</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CONTACTOS AUXILIARES</t>
+          <t>SPD SUB BASE VALV NCA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -652,7 +650,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -661,13 +659,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>71-030630-25</t>
+          <t>K065603349</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CABLE,PWR,MPE,25FT,FL</t>
+          <t>VALVULA SELENOIDE MOD K065603349</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -689,13 +687,13 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>72218BN3TN00</t>
+          <t>L6156310249</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALVULA DE 3/8, LATON, DOS VIAS 0-100PSI NC DIRECT LIFT SKINNER 2 WEG MAGN VENTIEL</t>
+          <t>VALVULA PARKER SCHRADER BELLOWS DE 4 VIAS CON ESCAPE INDEPENDIENTE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -708,7 +706,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -717,13 +715,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A7727F24</t>
+          <t>P1D-B100MCE1300NGNNN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOBINAS DE 24 VDC</t>
+          <t>CILINDRO NEUMATICO SERIE P1D 100mm BORE X1300mm STROKE MONTAJE TRUNION PUERTO NPTF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -745,13 +743,13 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K593-720</t>
+          <t>05R211AD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOBINA CUADRADA 220 V 60HZ</t>
+          <t>REGULADOR DE PRESION SERIE 05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -764,7 +762,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -773,13 +771,13 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PA40SAG8S080S</t>
+          <t>0859170006</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VALVULA ANGULAR ABV SR NCA DN40 1-1/2"</t>
+          <t>CABLE PARA SENSOR..</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -801,13 +799,13 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XLG20600AB64BS</t>
+          <t>1640812</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VALVULA SKINNER (XLG20600AB64BS)</t>
+          <t>SACC_VQ_3CON_0.75_A_L12/24 PHOENIX CONTACT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -820,7 +818,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -829,13 +827,13 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7F5090242055</t>
+          <t>1664306</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VENTILADOR 24 VDC 150X150</t>
+          <t>CARCAZA EMPOTRADA CON TUERCA AISZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -848,7 +846,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -857,13 +855,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>051-KR012-00175</t>
+          <t>P32FA92EGMN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KIT DE EMPAQUES DE VASTAGO DE 1 3/4" DE LA SERIE J</t>
+          <t>FILTRO STD. 1/4" MANUAL Modelo P32FA92EGMN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -872,7 +870,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>pza</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -885,13 +883,13 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OE4-SBHS-6K</t>
+          <t>P3TFA9BWGAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switch de presion de 50-100 psi parker modelo OE4-SBHS-6K</t>
+          <t>1-1/2 LIQUID SEPARATOR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -904,7 +902,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -913,13 +911,13 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12-081</t>
+          <t>P8S-TMA08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IPS PERFIL 14 X 80</t>
+          <t>SENSOR MOUNT. P1D-T 125-320</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -928,11 +926,11 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MTS.</t>
+          <t>PZA</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -941,13 +939,13 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24-135-5</t>
+          <t>PK1502MA05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IPS M5x35 BUTTON HEAD SCREW No PARTE 24-135-5</t>
+          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK1502MA05)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -960,7 +958,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -969,13 +967,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05R211AD</t>
+          <t>PS401165MCP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>REGULADOR DE PRESION SERIE 05</t>
+          <t>MANIFUL DE 3/8 NPT MARCA PARKER MODELO PS401165MCP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -988,7 +986,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1025,13 +1023,13 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100-C09KF10</t>
+          <t>P1M-6QRN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CONTACTOR 1 NO BOBINA 230 VAC 5-60 HZ</t>
+          <t>KIT DE SELLOS P/CIL P1M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1044,7 +1042,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1053,13 +1051,13 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>194E-A-P11</t>
+          <t>P2A12RD25-1P-01-E</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CONTACTO MODELO 194E-A-P11</t>
+          <t>VALVULA NEUMATICA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1072,7 +1070,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1081,13 +1079,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>800FM-SB32</t>
+          <t>1527993</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SELECTOR 3 POS. SIN CONTACTOS MCA ALLEN BRADLEY</t>
+          <t>Conector DIN de válvula, 3 polos, construcción BI, sin conectar, conexión por tornillo, prensaestopas Pg</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1096,11 +1094,11 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PZA.</t>
+          <t>PZA</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1109,13 +1107,13 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>800T-XD2</t>
+          <t>P3TFA92WAAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BLOCK DE CONTACTOS ADICIONALES MODELO 800T-XD2</t>
+          <t>SEPARADORES DE AGUA DE 1/4 MODELO P3TFA92WAAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1128,7 +1126,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1137,13 +1135,13 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PTL-19-427</t>
+          <t>P3TFA96WDAN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PTL-19-427 ETIQUETA PARA CABLE AUTOLAMINABLE CAL 10-12</t>
+          <t>SEPARADOR DE AGUA PUERTO DE 3/4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1156,7 +1154,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1165,13 +1163,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VM26-PM</t>
+          <t>P8S-EPFXS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Conector con cable de IO</t>
+          <t>SENSOR PNP PARA CILINDRO P1Q</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1184,7 +1182,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1193,13 +1191,13 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>444610W</t>
+          <t>PK050MP001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VALVULA SOLENOIDE USO GENERAL 1/2</t>
+          <t>KIT DE EMPAQUES PARA VASTAGO MARCA PARKER MODELO PK050MP001</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1221,13 +1219,13 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7K803</t>
+          <t>PS742P</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KIT DE SELLOS PARA VALVULA DE 1/2"</t>
+          <t>FILT CAP KIT PARA LUBRICADOR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1249,13 +1247,13 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>H111C1</t>
+          <t>1681305</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BOBINA PARA VALVULA SKINER</t>
+          <t>CON.DIN 3P C/LED A 100/120 VAC/DC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1268,7 +1266,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1277,13 +1275,13 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0104030108</t>
+          <t>1692857</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SELLO PARA EMBOLO</t>
+          <t>SACB-4/4-C CAJA SE SENSORES Y ACTUADORES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1305,13 +1303,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>052-AG101-00800</t>
+          <t>1771011</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ANILLO CONTRA GIRO MILLER.</t>
+          <t>CONECTO ENCHUFABLE CONSTRUCCION B6 HEMBRA HC-B 6-EBUS  PHOENIX CONTACT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1324,7 +1322,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1333,13 +1331,13 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>052-PS025-00800</t>
+          <t>1771202</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SELLO DE EMB D/BUNA MILLER</t>
+          <t>SOPOR CONEXION HEMBRA DE 10 POLOS REF HC-B 10-EBUS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1361,13 +1359,13 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>090-ES009-00800</t>
+          <t>1771257</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EMPAQUE FINAL SER A Y J MILLER</t>
+          <t>CARCAZA AEREA PHOENIX</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1389,13 +1387,13 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1455360000</t>
+          <t>1771451</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MTG BRKT W/PIN 100MM HM MODELO 1455360000  CLEVIS </t>
+          <t>CONECTOR HC-B-10-KML-52/M1PG16MCA PHOENIX CONTACT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1417,13 +1415,13 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HF22L10VQ</t>
+          <t>1771723</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Elemento filtrante modelo HF22L10VQ</t>
+          <t>SOPORTE DE CONTACTOS HEMBRAS HEAVY B24 PHOENIX CONTACT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1436,7 +1434,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -1445,13 +1443,13 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SDV-10410-5C</t>
+          <t>1772528</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SDV10-1P4S-1C</t>
+          <t>CONECTOR MACHO HC-D 64-ESTC MARCA PHOENIX CONTACT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1464,7 +1462,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1473,13 +1471,13 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20-040</t>
+          <t>2263007</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IPS SUJETADOR UNIVERSAL 20</t>
+          <t>SF-SKBI 64</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1492,7 +1490,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -1501,13 +1499,13 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1.50BC2MAU14A0.59</t>
+          <t>2281665</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CILINDRO NEUMATICO SERIE 2MA</t>
+          <t>FLKM-D50 SUB/S/LA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1520,7 +1518,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -1529,13 +1527,13 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EZ11NBB553A</t>
+          <t>SMH50-1PC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VALVULA NEUMATICA EZ11NBB553A</t>
+          <t>Sensores de posición  NO PNP modelo SMH50-1PC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1557,13 +1555,13 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>P1M-6QRN</t>
+          <t>0712123</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KIT DE SELLOS P/CIL P1M</t>
+          <t>TCP 0,25A INTERUPTORES DE PROTECCION</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1576,7 +1574,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -1585,13 +1583,13 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2.50CC2HLUVS14AC1.1</t>
+          <t>0712275</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CILINDRO HIDRAULICO</t>
+          <t>TCP 6A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1604,7 +1602,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -1613,13 +1611,13 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6C10-025X8</t>
+          <t>0712314</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ELEMENTO FILTRANTE PARKER CAJA CON 8 PZAS</t>
+          <t>TCP 10A INTERRUPTOR DE PROTECCION BRAKER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1632,7 +1630,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -1641,13 +1639,13 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>800FM-P4</t>
+          <t>0800346</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OPERADOR PARA LUZ PILOTO METALICO COLOR ROJO MCA ALLEN BRADLEY</t>
+          <t>ETIQUETA DE SEGURIDAD CON ADHESIVO ESPECIAL, ROLLO, COLOR PLATA, SIN ROTULAR MARCA PHOENIX CONTACT.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1669,13 +1667,13 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>800FP-P3</t>
+          <t>0800420</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OPERADOR DE LUZ PILOTO PLASTICO COLOR VERDE</t>
+          <t>MANGUITO PARA SEÑALIZACION DEL 0-4 CAL.16 (BOLSAS 100 PZAS POR NUMERO)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1688,7 +1686,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -1697,13 +1695,13 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>855T-L24</t>
+          <t>0800458</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FOCO MODELO 855T-L24 6.5 W</t>
+          <t>Etiqueta, Tarjeta, blanco, sin rotular, rotulable con: THERMOMARK CARD, Tipo de montaje: Pegado, Sup</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1716,7 +1714,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -1725,13 +1723,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>48358001N7</t>
+          <t>0800462:0002</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BOBINA 28 VDC MAX (24 VNOM) 32 MM CLASE F, EEX MODELO 48358001N7</t>
+          <t>MANGUITOS PARA SEÑALIZACION DE CONDUCTORES PARA NUMERO "2"</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1744,7 +1742,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>211</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -1753,13 +1751,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PA50SAG9S100S</t>
+          <t>0801371</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VALVULA ANGULAR ABV SR NCA DN40 2"</t>
+          <t>RIBBON PARA THERMOMARK  0801371</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1772,7 +1770,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -1781,13 +1779,13 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>052-PS025-00400</t>
+          <t>0801660</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SELLO DEL EMB. D/BUNA MILLER..</t>
+          <t>CES-B10-SFFS-PLBK - Marco de obturación</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1800,7 +1798,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -1809,13 +1807,13 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>052-PS025-00600</t>
+          <t>0801666</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SELLO DEL EMB. D/BUNA MILLER....</t>
+          <t>CES-SRG-BK-4X4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1828,7 +1826,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -1837,13 +1835,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>090-ES009-00500</t>
+          <t>0818108</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SELLOS DE LAS TAPAS PARA CILINDROS NEUMATICOS DE 5" DE LA SERIE A</t>
+          <t>TIRA ZACK ROTULABLE DE 96 ROTULOS PARA CENTRO DE BORNES UC-TM 5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1856,7 +1854,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -1865,13 +1863,13 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1.00CFP3LLRS19AC2.55</t>
+          <t>0828740</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">cilindro hidraulico serie 3L camisa de 1" de diametro y 2.55" de carrera     nota: S= PUERTOS HEAD &amp; CAP EN POSICION 4 </t>
+          <t>UCT-TM 8 -  Marcador para bornes, Estera, blanco, sin rotular, rotulable con: Thermomark C+, Thermomark C,</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -1884,7 +1882,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -1893,13 +1891,13 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24-312-4</t>
+          <t>0828767</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>24-312-4 IPS TORNILLO M4 X 12</t>
+          <t>Marcador de cables, Tarjeta, blanco, sin rotular, rotulable con: Thermomark C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1912,7 +1910,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -1921,13 +1919,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24-325-5</t>
+          <t>2748674</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IPS M5X20 SOCKET HEAD MOD. 24-325-5</t>
+          <t>PROTECTOR PHOENIX CONTACT MODELO UAK-2-PE/S-120AC-BE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -1949,13 +1947,13 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1527993</t>
+          <t>PK080MP001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Conector DIN de válvula, 3 polos, construcción BI, sin conectar, conexión por tornillo, prensaestopas Pg</t>
+          <t>KIT DE SELLOS MARCA PARKER.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1968,7 +1966,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -1977,13 +1975,13 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>H21WXBG2B9000FC</t>
+          <t>PK2002MA01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VALVULA PARKER MODELO H21WXBG2B900FC</t>
+          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK2002MA01)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1996,7 +1994,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -2005,13 +2003,13 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>K022112</t>
+          <t>PK2002MA05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SPD SUB BASE VALV NCA</t>
+          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK2002MA05)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2024,7 +2022,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -2033,13 +2031,13 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>K065603349</t>
+          <t>PK3202MA01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VALVULA SELENOIDE MOD K065603349</t>
+          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK3202MA01)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2052,7 +2050,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -2061,13 +2059,13 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>L6156310249</t>
+          <t>PK5002MA01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VALVULA PARKER SCHRADER BELLOWS DE 4 VIAS CON ESCAPE INDEPENDIENTE</t>
+          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK5002MA01)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2080,7 +2078,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -2089,13 +2087,13 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>P2A12RD25-1P-01-E</t>
+          <t>PK5002MA05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VALVULA NEUMATICA</t>
+          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK5002MA05)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2117,13 +2115,13 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>P3TFA92WAAN</t>
+          <t>PS4517P</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SEPARADORES DE AGUA DE 1/4 MODELO P3TFA92WAAN</t>
+          <t>VALVULA NCA. SERIE B4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2136,7 +2134,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -2145,13 +2143,13 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>800T-1TZ</t>
+          <t>1771118</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ESTACION DE BOTONES</t>
+          <t>CARCASA AREA LAT.  PHOENIX CONTACT HC-B6-TFL-43/M1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -2164,7 +2162,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -2173,13 +2171,13 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>321-H36</t>
+          <t>1771325</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VALVULA DE ALTA PRESION LUCIFER</t>
+          <t>PANEL MOUNTAING BASE CHC-B-10-AMQ CARCAZA EMPOTRADA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -2192,7 +2190,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -2201,13 +2199,13 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PF32BNP00</t>
+          <t>1771338</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MEDIDOR DE FLUJO DE 2" DE 200GPM 4-20 MA</t>
+          <t>CARC.EMPOT.C/BR.LONG.S/TAPA REF.HC-B 10AML</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2229,13 +2227,13 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ZB09</t>
+          <t>2281652</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VALVULA SOLENOIDE SCEM 2VIAS 2 POSICIONES 240V/60Hz</t>
+          <t>FLKM-D37 SUB/S/L</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2248,7 +2246,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -2257,13 +2255,13 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7F5081203100</t>
+          <t>2293446</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>VENTILADOR DE 120VAC 204X204</t>
+          <t>ADAPTADOR FRONTAL PARA PLC AB SLC 500 1746OA16 (OW16)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2285,13 +2283,13 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>026-57660-H</t>
+          <t>PXBB1921</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VLV HCA A4D0232030302B1G0Q VALVULA DIRECCIONAL HIDRAULICA CENTROS CERRADOS DOBLE BOBINA 24 VDC</t>
+          <t>PARKER MODELO PXBB1921</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2313,13 +2311,13 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>051-RS014-00138</t>
+          <t>RG02MA0065</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SELLO DEL VASTAGO DE 1" 3/8 DE LA SERIE A</t>
+          <t>KIT D/SELLOS GUIA VAST CIL 2MA (RG02MA0065)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2332,7 +2330,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -2341,13 +2339,13 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>051-WP001-00175</t>
+          <t>RG0MP00201</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SELLO LIMPIADOR MILLER.</t>
+          <t>KIT D/SELLOS GUIA VAST CIL MP.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2360,7 +2358,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -2369,13 +2367,13 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>052-PS025-00325</t>
+          <t>0444019</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EMPAQUES DEL EMBOLO PARA CILINDRO  3 1/4" DE LA SERIE A</t>
+          <t>CLEMA DE TIERRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -2388,7 +2386,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -2397,13 +2395,13 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>052-RR102-00800</t>
+          <t>0800433</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ANILLO RETEN DE EMBOLO DE 8" DE LA SERIE A</t>
+          <t>PMH 0:GROSSBUCHSTABEN (TODAS LAS LETRAS DE LA A A LA Z)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2416,7 +2414,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -2425,13 +2423,13 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2.00TRDHBUS17M47.0</t>
+          <t>0801620</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CILINDRO HIDRAULICO SERIE RDH</t>
+          <t>CES-SRG-BK-10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2444,7 +2442,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -2453,13 +2451,13 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CMD09-2</t>
+          <t>0801670</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CONEC. CODO 3/8 SERIE (BX 10)</t>
+          <t>CES-SRG-BK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2472,7 +2470,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -2481,13 +2479,13 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2.504RLP4X1.0</t>
+          <t>0801675</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CILINDRO NEUMATICO SERIE LP</t>
+          <t>CES-STPG-GY-5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2500,7 +2498,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -2509,13 +2507,13 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3.25DB2MAU34A6.</t>
+          <t>0801679</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CILINDRO NEUMATICO SERIE 2MA (3.25DB2MAU34A6.)</t>
+          <t>CES-STPG-GY-8 - Pasacables</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -2528,7 +2526,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -2537,13 +2535,13 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MMDVA1</t>
+          <t>0801681</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SILENCIADOR SER.MODUFLEX (BX 10)</t>
+          <t>CARRIL SIMÉTRICO, MATERIAL:ACERO, SIN PERFORAR, ALTURA 7.5MM, ANCHURA 35MM, LONGITUD 2M</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -2552,11 +2550,11 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>MTS.</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -2565,13 +2563,13 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>P32FA92EGMN</t>
+          <t>0801733</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FILTRO STD. 1/4" MANUAL Modelo P32FA92EGMN</t>
+          <t>RIEL DIN DE PHOENIX CONTACT:Carril simétrico perforado, según EN 60715, material: Acero, galvanizado, pasivado de capa gruesa, Perfil estándar, color: plata, Variante de embalaje con 25 unidades (50 m</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -2580,11 +2578,11 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>pza</t>
+          <t>MTS.</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -2593,13 +2591,13 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>800FM-HB32</t>
+          <t>0803931</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SELECTOR DE 3 POSICIONES CON RETORNO AL CENTRO MODELO 800FM-HB32</t>
+          <t>MM-WML 3 (EX10)R C1 WH/BK  (p/Thermofox) Etiqueta de marcador de cables, Rollo, blanco, rotulable con: THERMOFOX: sin impresión, clase de montaje: pegado, superficie útil: sin fin x 10 mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -2621,13 +2619,13 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>800F-X10</t>
+          <t>0804155</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CONTACTO NO</t>
+          <t>EO-AB/UT/LED/15 Toma de corriente</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2640,7 +2638,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -2649,13 +2647,13 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>800H-N12</t>
+          <t>0808244</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PROTECCION PARA BOTON DE 30 MM</t>
+          <t>TIRAS DE ROTULACION MODELO 0808244</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2668,7 +2666,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -2677,13 +2675,13 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>71-030630-10</t>
+          <t>0819398</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CABLE.PWR,MPE 10 FT FL</t>
+          <t>TIRA ROTULABLE PARA MANGUITOS DE 32 UNIDADES UC-WMT (15X4)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2696,7 +2694,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -2705,13 +2703,13 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>71-030631-25</t>
+          <t>0827448</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CABLE, FDBK. MPE, ARIES 25 FT</t>
+          <t>Soporte para señalización, negro, sin rotular, Tipo de montaje: Tornillos, remaches, Diámetro: 22 mm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2724,7 +2722,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -2733,13 +2731,13 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>121K3306</t>
+          <t>0828732</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LUCIFER 121K3306</t>
+          <t>Marcador para bornes, Estera, blanco, sin rotular, rotulable con: TOPMARK NEO, TOPMARK LASER, BLUEMARK ID COLOR, BLUEMARK ID, BLUEMARK CLED, THERMOMARK PRIME, THERMOMARK CARD 2.0, THERMOMARK CARD, cla</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2752,7 +2750,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -2761,13 +2759,13 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7321BDN90</t>
+          <t>0828772</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CUERPO DE VALVULA DE 1" USO GENERAL</t>
+          <t>LAMINA PARA ROTULAR EN THERMOMARK CARD DE 24 UNIDADES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2780,7 +2778,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -2789,13 +2787,13 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7321GBN99N00</t>
+          <t>0828778</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VALVULA SKINNER 2" N.C. 2 VIAS PROPOSITO GENERAL</t>
+          <t>Rótulo para encajar, Tarjeta, blanco, sin rotular, rotulable con: THERMOMARK CARD PLUS, THERMOMARK C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -2808,7 +2806,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -2817,13 +2815,13 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C111C1</t>
+          <t>0829536</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BOBINA PARA VALVULA SKINNER</t>
+          <t>Protección contra contactos accidentales, Codo, transparente, sin rotular, Tipo de montaje: Encajar</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2836,7 +2834,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -2845,13 +2843,13 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7F5090244230</t>
+          <t>0903033</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VENTILADOR DE 24VDC 250X250</t>
+          <t>EC-E4 2A - Interruptor de protección electrónico, contacto de señales: 1 contacto cerrado, corriente nominal: 2 A; Marca Phoenix Contact</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2864,7 +2862,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -2873,13 +2871,13 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>051-RS014-00175</t>
+          <t>2769585</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SELLO VASTAGO D/BUNA  MILLER</t>
+          <t>MCR-CP-I-I-00 AMPLIFICADOR</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -2892,7 +2890,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -2901,13 +2899,13 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>090-ES009-00325</t>
+          <t>2798682</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SELLOS DE LAS TAPAS PARA CILINDRO 3 1/4" DE LA SERIE A</t>
+          <t>PROTECTOR PHOENIX CONTACT MODELO UAK 2-PE/S-X-120AC-ST</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -2920,7 +2918,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -2929,13 +2927,13 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>090-ES009-00400</t>
+          <t>2864532</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EMPAQUE FINAL SER. A Y J MILLER..</t>
+          <t>MCR-FL-HT-TI-EX Convertidor de temperatura de cabecera MCR, programable, seguridad intrínseca, para termoresistencias, termopares, potenciómetros de control y transmisores de tensión. Para termoresist</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -2948,7 +2946,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -2957,13 +2955,13 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>301008000</t>
+          <t>2866404</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KIT DE EMPAQUES PARA CILINDRO</t>
+          <t>TRIO-PS/3AC/24DC/40 Fuente de alimentación conmutada en primario TRIO POWER para montaje sobre carril, entrada: trifásica, salida: 24 V DC/40 A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -2985,13 +2983,13 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1460200</t>
+          <t>2866446</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Carcasa aérea HEAVYCON B24, para bloqueo longitudinal, altura 76 mm, con prensaestopas 1x Pg21, salida de cables lateral</t>
+          <t>MINI-PS-100-240AC/24DC/1.3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3013,13 +3011,13 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2.5J2HKT14A10.00</t>
+          <t>2867296</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2.5J2HKT14A10.00</t>
+          <t>RAD-ISM-900-DATA-BD-BUS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -3041,13 +3039,13 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FC702-4G</t>
+          <t>0911160</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VALVULA  CONTROL DE FLUJO  OP70 TOCCO</t>
+          <t>PORTAFUSIBLE 380V DE 2-16A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3060,7 +3058,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -3069,13 +3067,13 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>K022113</t>
+          <t>0913045</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VALVULA PARKER K022113 DOBLE SELENOIDE</t>
+          <t>FUSIBLE DE 10 AMPS.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3088,7 +3086,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -3097,13 +3095,13 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>K352164</t>
+          <t>0921011</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KIT PARKER K352164</t>
+          <t>Cabeza portafusible, corriente nominal: 6,3 A, longitud: 33,1 mm, anchura: 6,1 mm, altura: 45,7 mm, color: negro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3116,7 +3114,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -3125,13 +3123,13 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>K4515N18160</t>
+          <t>2715995</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANOMETRO p/regulador P31 DE 40mm caratula 1/8" NPT 0-160PSI </t>
+          <t>BORNES DE 3 CUERPOS PARA DETECTORES CON INDICADOR ROJO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -3153,13 +3151,13 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>L073400075</t>
+          <t>2866381</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ABRAZADERA PARA SUJETAR DETECTOR PARKER PISTON DIAM 3/4" .75 SRM MTG. KIT</t>
+          <t>TRIO-PS/1AC/24DC/20 Fuente aliment. carr. simétr., conmutada primario, monofásica, salida: 24 V DC / 20 A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3172,7 +3170,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -3181,13 +3179,13 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>P1C-4NMCA</t>
+          <t>2958325</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CLEVIS BRACKET P/CIL NICO</t>
+          <t>UM-ULA-400AC</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3200,7 +3198,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -3209,13 +3207,13 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>P1C-4PMCA</t>
+          <t>1207860</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SOPORTE GIRATORIO "GA"</t>
+          <t>DATA-TWIST  11 PELACABLES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3228,7 +3226,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -3237,13 +3235,13 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>140M-C2E-C20</t>
+          <t>3204010</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ARRANCADOR MANUAL Y PROTECTOR 10-16 AMP</t>
+          <t>QT 1.5</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3265,13 +3263,13 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1492-CAB010-A62</t>
+          <t>3206034</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CABLE DE INTERFAZ A RELEVADORES MODELO 1492-CAB010-A62</t>
+          <t>D-QT 2.5 TAPA FINAL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3284,7 +3282,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -3293,13 +3291,13 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1794-PS3</t>
+          <t>750002//</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FUENTE DE VOLTAJE PARA FLEX I/O</t>
+          <t>Juego de terminales PNOZ s Setscrew terminals 12,5mm por resorte  (2A999990,  2A999991, 2A999992, 2A999993)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3312,7 +3310,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -3321,13 +3319,13 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>800T-XA2</t>
+          <t>773110</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Contactos NO MODELO 800T-XA2</t>
+          <t>PNOZ m0p base unit not expandable, PNOZmulti Classic, dispositivobase, no ampliable, 4 salidas por semiconductor seguras, 2 salidas de relé seguras; Marca Pilz</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3340,7 +3338,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -3349,13 +3347,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>H111P3</t>
+          <t>750003//</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BOBINA 120 VAC A PRUEBA DE EXPLOSIONES Skinner Coil 110/50, 120/60</t>
+          <t>Mypnoz Screw terminals 3 polos sets 17.5.mm x1,x2,x3,x4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3368,7 +3366,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -3377,13 +3375,13 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>051-WP001-00138</t>
+          <t>12903720</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SELLO LIMPIADOR DEL VASTAGO DE 1" 3/8 DE LA SERIE A</t>
+          <t>MOTOR MARCA WEG HP5, 3F, 4P, 184TC, C/B, 230/460V, 60hz, CA, TEFC</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3396,7 +3394,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -3405,13 +3403,13 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>052-PS025-00500</t>
+          <t>1608740000</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EMPAQUES DEL EMBOLO DE 5" DE LA SERIE A</t>
+          <t>END PLATE ZAP/TW 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3424,7 +3422,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -3433,13 +3431,13 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1488970125</t>
+          <t>BAM00A2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SENSOR PARA CILINDRO PARKER MOD. 1488970125</t>
+          <t>MOUNTING CLAMP FOR TUBULAR SENSOR</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -3452,7 +3450,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -3461,13 +3459,13 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>171-KB003-00250</t>
+          <t>BAM00CH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KIT DE SELLOS MILLER</t>
+          <t>BES120KB5F  BASE DE MONTAJE PARA SENSOR DE 12 MM</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -3480,7 +3478,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -3489,13 +3487,13 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>691750</t>
+          <t>BCC06M4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>COIL 120 VCA HIRSH/K16-90-6</t>
+          <t>BCC M434-0000-2A-000-41X475-000</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -3508,7 +3506,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -3517,13 +3515,13 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1640812</t>
+          <t>BCC06YA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SACC_VQ_3CON_0.75_A_L12/24 PHOENIX CONTACT</t>
+          <t>CONECTOR PARA PUERTO ESTANDAR M12 HEMBRA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -3536,7 +3534,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -3545,13 +3543,13 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1.06BFDSR04.0</t>
+          <t>BES02KJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CILINDRO NEUMATICO MODELO 1.06BFDSR04.0</t>
+          <t>SENSOR INDUCTIVO MARCA BALLUFF MODELO BES M18ML PSC50A S04G W</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -3573,13 +3571,13 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>F0-040.1251V</t>
+          <t>BES516324E5CS49</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PISTON NEUMETICO DE 1/4" MCA. BIMBA</t>
+          <t>SENSOR PNP NORMALMENTE ABIERTO MODELO BES516324E5CS49</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -3592,7 +3590,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -3601,13 +3599,13 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MPS-ACCK8</t>
+          <t>ROACA06B16C010F</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MPS-ACCK8 BRACKET (MPS-33)</t>
+          <t>RECEPTACULO BALLUFF MODELO ROA-CA-06-B-16C-010F</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -3629,13 +3627,13 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MSFG-24DC/42AC</t>
+          <t>1769-RTB40DIO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BOBINA PARA VALVULA FESTO</t>
+          <t>CONECTOR DE CONEXION MODELO 1769-RTB40DIO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -3657,13 +3655,13 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>P1C-4NMBA</t>
+          <t>1SFA616923R1118</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BRIDA PARA CILINDRO ISO P1D-B 63mm</t>
+          <t>FOCO PARA MODULO DE 5W A 115 VAC</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -3676,7 +3674,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -3685,13 +3683,13 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>P8S-TMA08</t>
+          <t>932679Q</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SENSOR MOUNT. P1D-T 125-320</t>
+          <t>Elemento de repuesto para filtro en línea de alta presión serie 50P</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -3700,7 +3698,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -3713,13 +3711,13 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PS401165MCP</t>
+          <t>1608860000</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MANIFUL DE 3/8 NPT MARCA PARKER MODELO PS401165MCP</t>
+          <t>TERMINAL BLOCK JUMPER, 2WAY, 5.1MM</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -3732,7 +3730,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -3741,13 +3739,13 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SMH50-1PC</t>
+          <t>1684247</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sensores de posición  NO PNP modelo SMH50-1PC</t>
+          <t>CARCAZA DE ACOPLAMIENTO LIBRE CAPERUZA DE PLASTICO RECTA PANTALLADO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3769,13 +3767,13 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0800458</t>
+          <t>1706010000</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Etiqueta, Tarjeta, blanco, sin rotular, rotulable con: THERMOMARK CARD, Tipo de montaje: Pegado, Sup</t>
+          <t>CLEMA ZDU 2.5-2/3AN</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3788,7 +3786,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -3797,13 +3795,13 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0801666</t>
+          <t>BCS00LM</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CES-SRG-BK-4X4</t>
+          <t>BCS M18BBG2-PSC15H-S04K</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -3816,7 +3814,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -3825,13 +3823,13 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0818108</t>
+          <t>BDNTPTEAA01</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TIRA ZACK ROTULABLE DE 96 ROTULOS PARA CENTRO DE BORNES UC-TM 5</t>
+          <t>TEE DE 7/8 DE 4 POLOS BDN T-PTE-AA-01</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3844,7 +3842,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -3853,13 +3851,13 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0828740</t>
+          <t>BES0086</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>UCT-TM 8 -  Marcador para bornes, Estera, blanco, sin rotular, rotulable con: Thermomark C+, Thermomark C,</t>
+          <t>SENSOR INDUCTIVO M18</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3872,7 +3870,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -3881,13 +3879,13 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>P3TFA9BWGAN</t>
+          <t>BES02N3</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1-1/2 LIQUID SEPARATOR</t>
+          <t>BES M08EH1-NSC20B-S04G-S  Sensor inductivo Steel Fac</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3900,7 +3898,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -3909,13 +3907,13 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PK1502MA05</t>
+          <t>BES02ZE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK1502MA05)</t>
+          <t>BES M18MN-USU80B-S21G</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -3937,13 +3935,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PS742P</t>
+          <t>BES22BS1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FILT CAP KIT PARA LUBRICADOR</t>
+          <t>Accesorio de mantaje para  sensor</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3965,13 +3963,13 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0712123</t>
+          <t>BESA12-CM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TCP 0,25A INTERUPTORES DE PROTECCION</t>
+          <t>Aditamento M12x1 "Cushioned Prox Mount"</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -3984,7 +3982,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -3993,13 +3991,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0800462:0002</t>
+          <t>BLES51PA5F00PK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MANGUITOS PARA SEÑALIZACION DE CONDUCTORES PARA NUMERO "2"</t>
+          <t>BLES-51-PA-5-F00-PK</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -4012,7 +4010,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>211</v>
+        <v>2</v>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
@@ -4021,13 +4019,13 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0801371</t>
+          <t>BOS00EL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>RIBBON PARA THERMOMARK  0801371</t>
+          <t>BLS 18KF-XX-1LT-L-02</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -4049,13 +4047,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0828767</t>
+          <t>ZBVB4</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Marcador de cables, Tarjeta, blanco, sin rotular, rotulable con: Thermomark C</t>
+          <t>LUZ ROJA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -4068,7 +4066,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -4077,13 +4075,13 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0828800</t>
+          <t>P3TFA98WEAN</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Rótulo de plástico, Tarjeta, blanco, sin rotular, rotulable con: THERMOMARK CARD PLUS, THERMOMARK CARD, Tipo de montaje: Pegado, Superficie útil: 27 x 18 mm  PLANTILLA ETIQUETAS PARA BOTONERIA 21 pzas</t>
+          <t>SEPARADOR DE LIQUIDOS 1 PULGADA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -4096,7 +4094,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -4105,13 +4103,13 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2748674</t>
+          <t>PR4506Q</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PROTECTOR PHOENIX CONTACT MODELO UAK-2-PE/S-120AC-BE</t>
+          <t>ELEMENTO FILTRANTE</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -4124,7 +4122,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -4133,13 +4131,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2866404</t>
+          <t>SWC30M30GZ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TRIO-PS/3AC/24DC/40 Fuente de alimentación conmutada en primario TRIO POWER para montaje sobre carril, entrada: trifásica, salida: 24 V DC/40 A</t>
+          <t>ELEMENTO FILTRANTE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -4152,7 +4150,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -4161,13 +4159,13 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2866459</t>
+          <t>_00221844</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TRIO-PS/3AC/24DC/10 Fuente Trio trifasica de 24 vdc a 10 amp</t>
+          <t>EV 2/2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -4189,13 +4187,13 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PVP4836K9R2M11</t>
+          <t>_00783579</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>METRIC PISTON PUMP</t>
+          <t>CONECTOR</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -4208,7 +4206,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -4217,13 +4215,13 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>D3W2CNYC</t>
+          <t>01010505</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>VALVULA HCA DIRECCIONAL (D3W2CNYC)</t>
+          <t>CAJA FS DE 1/2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -4236,7 +4234,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -4245,13 +4243,13 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>x.x801733</t>
+          <t>0129521</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Riel Din  perforado, anchura: 35 mm, altura: 7,5 mm, según EN 60715, material: Acero, galvanizado, pasivado de capa gruesa, longitud: 2000 mm</t>
+          <t>M24 Delta Protekt Nord-Lock Bolt Securing Washer/Pair</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -4264,7 +4262,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -4273,13 +4271,13 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PK080MP001</t>
+          <t>2523T74</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KIT DE SELLOS MARCA PARKER.</t>
+          <t>RUEDA PARA ESTRUCTURA DE ALIMENTADOR DE TAPAS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -4288,7 +4286,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -4301,13 +4299,13 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PK2002MA05</t>
+          <t>26-420-8P</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK2002MA05)</t>
+          <t>IPS TRESPA GRIS 8MM HOJA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -4320,7 +4318,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -4329,13 +4327,13 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PK5002MA01</t>
+          <t>2701815</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK5002MA01)</t>
+          <t>AXIOLINE F , ACOPLADOR DE BUS , PROFINET , HEMBRA RJ45  , VELOCIDAD DE TRANSMISION EN EL BUS LOCAL : 100MBIT/S INDICE DE PROTECCION : IP20 , INCLUIDOS MODULO BASE DE BUS Y CONECTOR AXIOLINE F</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -4344,11 +4342,11 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
@@ -4357,13 +4355,13 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PK5002MA05</t>
+          <t>10M9531</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK5002MA05)</t>
+          <t>Terminal de Anillo, M3.5, 6, Serie SCOTCHLOK, 14 AWG, Polyolefin</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -4376,7 +4374,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -4385,13 +4383,13 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PXBB1921</t>
+          <t>100-KFC40</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PARKER MODELO PXBB1921</t>
+          <t>CONTACTOS AUXILIARES MODELO 100-KFC40</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -4404,7 +4402,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
@@ -4413,13 +4411,13 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RG02MA0065</t>
+          <t>1020100000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS GUIA VAST CIL 2MA (RG02MA0065)</t>
+          <t>Clema Paso Wdu4 26-10awg 35a Tornillo</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -4432,7 +4430,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
@@ -4441,13 +4439,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0800433</t>
+          <t>1061200000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PMH 0:GROSSBUCHSTABEN (TODAS LAS LETRAS DE LA A A LA Z)</t>
+          <t>TOPES PARA WDU</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -4460,7 +4458,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
@@ -4469,13 +4467,13 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>0801620</t>
+          <t>258083</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CES-SRG-BK-10</t>
+          <t>RETEN PARA FLECHA HPV20-RB35-RF-01R -A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -4497,13 +4495,13 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0801733</t>
+          <t>486265C4</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RIEL DIN DE PHOENIX CONTACT:Carril simétrico perforado, según EN 60715, material: Acero, galvanizado, pasivado de capa gruesa, Perfil estándar, color: plata, Variante de embalaje con 25 unidades (50 m</t>
+          <t>BOBINA 48 VCD POTENCIA 14 W</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -4512,11 +4510,11 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>MTS.</t>
+          <t>PZA</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
@@ -4525,13 +4523,13 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>0808244</t>
+          <t>6ES7390-1AE80-0AA0</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TIRAS DE ROTULACION MODELO 0808244</t>
+          <t>RAIL SIEMENS MODELO 6ES7390-1AE80-0AA0</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4544,7 +4542,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
@@ -4553,13 +4551,13 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>0828772</t>
+          <t>6GK1905-0FB00</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LAMINA PARA ROTULAR EN THERMOMARK CARD DE 24 UNIDADES</t>
+          <t>SIEMENS MODELO 6GK1905-0FB00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4572,7 +4570,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
@@ -4581,13 +4579,13 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>0829536</t>
+          <t>800FM-LF5</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Protección contra contactos accidentales, Codo, transparente, sin rotular, Tipo de montaje: Encajar</t>
+          <t>Boton pulsador amarillo co indicador de 22mm</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -4600,7 +4598,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
@@ -4609,13 +4607,13 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>0903033</t>
+          <t>3RV1011-1CA15</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>EC-E4 2A - Interruptor de protección electrónico, contacto de señales: 1 contacto cerrado, corriente nominal: 2 A; Marca Phoenix Contact</t>
+          <t>INTERRUPTOR AUTOM. TAM. S00, PARA PROTECC. MOTOR, CLASE 10, DISP.A 1,8...2,5A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -4637,13 +4635,13 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>0911160</t>
+          <t>3SB34000C</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PORTAFUSIBLE 380V DE 2-16A</t>
+          <t>BLOQUE DE CONTACTOS NC CON TERMINAL DE TORNILLO</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -4656,7 +4654,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
@@ -4665,13 +4663,13 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2293446</t>
+          <t>5SL6104-7CC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ADAPTADOR FRONTAL PARA PLC AB SLC 500 1746OA16 (OW16)</t>
+          <t>INTERRUPTOR TERMOMAGNETICO 1P 4A P/RIEL 6KA 230/44VAC 60VDC0</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -4693,13 +4691,13 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1771118</t>
+          <t>5SL6316-7CC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CARCASA AREA LAT.  PHOENIX CONTACT HC-B6-TFL-43/M1</t>
+          <t>SIEMENS INTERRUPTOR TERMOMAG 3P 16A P/RIEL 6KA 230/44VAC 60VDC0</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -4721,13 +4719,13 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1771325</t>
+          <t>622-000-095</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PANEL MOUNTAING BASE CHC-B-10-AMQ CARCAZA EMPOTRADA</t>
+          <t>LXR-0000-046</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -4736,11 +4734,11 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
@@ -4749,13 +4747,13 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2281652</t>
+          <t>6ES7972-0BB12-0XA0</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FLKM-D37 SUB/S/L</t>
+          <t>CONECTOR PROFIBUS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4768,7 +4766,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -4777,13 +4775,13 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>P3TFA96WDAN</t>
+          <t>800FM-F2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SEPARADOR DE AGUA PUERTO DE 3/4</t>
+          <t>Boton pulsador de 22mm negro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4796,7 +4794,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
@@ -4805,13 +4803,13 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PK050MP001</t>
+          <t>800FM-SM22</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KIT DE EMPAQUES PARA VASTAGO MARCA PARKER MODELO PK050MP001</t>
+          <t>Selector 2 posiciones  22mm</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4833,13 +4831,13 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PS4517P</t>
+          <t>800T-H2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>VALVULA NCA. SERIE B4</t>
+          <t>SELECTOR DE DOS POSICIONES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4852,7 +4850,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
@@ -4861,13 +4859,13 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RG0MP00201</t>
+          <t>855E-24TL7</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS GUIA VAST CIL MP.</t>
+          <t>Control Tower Stack Light, 24V AC/DC, LED, Type: Steady, Clear</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4889,13 +4887,13 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0444019</t>
+          <t>8F6X-S</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CLEMA DE TIERRA</t>
+          <t>DESTORCEDOR DE 1/2 NPT FLEER CAMPANA</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -4908,7 +4906,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
@@ -4917,13 +4915,13 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>0801681</t>
+          <t>CTHW12ME</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CARRIL SIMÉTRICO, MATERIAL:ACERO, SIN PERFORAR, ALTURA 7.5MM, ANCHURA 35MM, LONGITUD 2M</t>
+          <t>CABLE THW #12 ME  NEGRO</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -4936,7 +4934,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
@@ -4945,13 +4943,13 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>0803931</t>
+          <t>CTHW18CM//BCO</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MM-WML 3 (EX10)R C1 WH/BK  (p/Thermofox) Etiqueta de marcador de cables, Rollo, blanco, rotulable con: THERMOFOX: sin impresión, clase de montaje: pegado, superficie útil: sin fin x 10 mm</t>
+          <t xml:space="preserve">CABLE THW CAL. 18 C. MTY  BLANCO </t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -4960,11 +4958,11 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>MTS.</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
@@ -4973,13 +4971,13 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>0819398</t>
+          <t>D-A73</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TIRA ROTULABLE PARA MANGUITOS DE 32 UNIDADES UC-WMT (15X4)</t>
+          <t>SENSOR PARA CILINDRO SMC</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4992,7 +4990,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
@@ -5001,13 +4999,13 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>0828732</t>
+          <t>E11419</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Marcador para bornes, Estera, blanco, sin rotular, rotulable con: TOPMARK NEO, TOPMARK LASER, BLUEMARK ID COLOR, BLUEMARK ID, BLUEMARK CLED, THERMOMARK PRIME, THERMOMARK CARD 2.0, THERMOMARK CARD, cla</t>
+          <t>Conector M12 para válvula tipo A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -5020,7 +5018,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
@@ -5029,13 +5027,13 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>0828778</t>
+          <t>F1-SU1Z UN</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Rótulo para encajar, Tarjeta, blanco, sin rotular, rotulable con: THERMOMARK CARD PLUS, THERMOMARK C</t>
+          <t>PEDAL METALICO SENCILLO DE ACCION RAPIDO CON PROTECCION 1NC</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -5048,7 +5046,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
@@ -5057,13 +5055,13 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2715995</t>
+          <t>GLANDULA DE 1/2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BORNES DE 3 CUERPOS PARA DETECTORES CON INDICADOR ROJO</t>
+          <t>GLANDULA DE PLASTICO DE 1/2"</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -5076,7 +5074,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
@@ -5085,13 +5083,13 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>D3W2CNTC</t>
+          <t>JZ-500 3C AWG20</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>VALVULA HCA DIRECCIONAL (D3W2CNTC)</t>
+          <t>MULTICONDUCTOR 3HILOS CALIBRE 20</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -5100,11 +5098,11 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>MTS.</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
@@ -5113,13 +5111,13 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PS575B49P</t>
+          <t xml:space="preserve">KB07309      </t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>KIT SOLENOID 24 VDC NON LOCKING 15 MMM</t>
+          <t>AD-T12, FOCO BA15D LED-120V-ROJO 12 LEDS 120 V</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -5132,7 +5130,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
@@ -5141,13 +5139,13 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>0712275</t>
+          <t>KB07601</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TCP 6A</t>
+          <t xml:space="preserve">LED AZUL 24V </t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -5160,7 +5158,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
@@ -5169,13 +5167,13 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>0712314</t>
+          <t>CTHW18CM//ROJO</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TCP 10A INTERRUPTOR DE PROTECCION BRAKER</t>
+          <t>CABLE FLEXANEL ROJO 18</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -5184,11 +5182,11 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>MTS.</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
@@ -5197,13 +5195,13 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>0800420</t>
+          <t>CUADRO ADH.3/4"</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MANGUITO PARA SEÑALIZACION DEL 0-4 CAL.16 (BOLSAS 100 PZAS POR NUMERO)</t>
+          <t>CUADRO ADHERIBLE DE 3/4" IT CAO75</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -5212,11 +5210,11 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PZA.</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>700</v>
+        <v>20</v>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
@@ -5225,13 +5223,13 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2864532</t>
+          <t>CUADRO ADHERIBLE 1"</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MCR-FL-HT-TI-EX Convertidor de temperatura de cabecera MCR, programable, seguridad intrínseca, para termoresistencias, termopares, potenciómetros de control y transmisores de tensión. Para termoresist</t>
+          <t>CUADRO ADHERIBLE 1"</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -5244,7 +5242,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -5253,13 +5251,13 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2866310</t>
+          <t>E11420</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TRIO-PS/1AC/24DC/5 FUENTE PHOENIX CONTACT</t>
+          <t>CABLE DE CONEXION</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -5272,7 +5270,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
@@ -5281,13 +5279,13 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2866446</t>
+          <t>E50S8-250-3-T-24</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MINI-PS-100-240AC/24DC/1.3</t>
+          <t>Encoder incremental , diam 50mm, flecha solida de 8mm, salida totem pole (NPN/PNP)  250 PPR, fases: A, B, Z, Alimentación: 12 a 24 VCC, con cable de 2 mts</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -5309,13 +5307,13 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2867296</t>
+          <t>FREIGHT COST / FLETE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>RAD-ISM-900-DATA-BD-BUS</t>
+          <t>COST OF SHIPPING (COSTO DE ENVIO DE MATERIAL)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -5328,7 +5326,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
@@ -5337,13 +5335,13 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>24-210-6</t>
+          <t>GLANDULA 3/4</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>IPS TORNILLO CABEZA PLANA M6 X 10</t>
+          <t>PLASTIC GLANDULA 3/4 PLASTICO</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -5356,7 +5354,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
@@ -5365,13 +5363,13 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1664306</t>
+          <t>GLANDULA METALICA 1/2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CARCAZA EMPOTRADA CON TUERCA AISZ</t>
+          <t>GLANDULA METALICA DE 1/2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -5384,7 +5382,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
@@ -5393,13 +5391,13 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1692857</t>
+          <t>GLANDULA METALICA 3/4</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SACB-4/4-C CAJA SE SENSORES Y ACTUADORES</t>
+          <t>GLANDULA METALICA DE 3/4</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -5412,7 +5410,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
@@ -5421,13 +5419,13 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1771202</t>
+          <t>HTS-PA-12</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SOPOR CONEXION HEMBRA DE 10 POLOS REF HC-B 10-EBUS</t>
+          <t>INDICADOR HTS-PA-12 IGUS 12MM</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -5449,13 +5447,13 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1771257</t>
+          <t>INST.1197</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CARCAZA AEREA PHOENIX</t>
+          <t>SUMINISTTRO E INSTALACION DE 45 M DE TUBERIA DE CONDUIT DE 1/2 Y 150 M DE CABLE PARA LA ALIMENTACION ELECTRICA A INTERRUPTOR DE 30 AMP EN EL AREA DE SCRAP EN PLANTA CLARIOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -5464,11 +5462,11 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
@@ -5477,13 +5475,13 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1772528</t>
+          <t>KB07518</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CONECTOR MACHO HC-D 64-ESTC MARCA PHOENIX CONTACT</t>
+          <t>LED 24V COLOR ROJO 12 LEDS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -5496,7 +5494,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
@@ -5505,13 +5503,13 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2263007</t>
+          <t>KB07519</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SF-SKBI 64</t>
+          <t xml:space="preserve">LED 24V AMARILLO  </t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -5524,7 +5522,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
@@ -5533,13 +5531,13 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1681305</t>
+          <t>KQ2H08-10</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CON.DIN 3P C/LED A 100/120 VAC/DC</t>
+          <t>CONECTOR RECTO DE 8MM MANG. A 10 MAN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -5552,7 +5550,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
@@ -5561,13 +5559,13 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1771011</t>
+          <t>LOTE DE MANGUERAS Y CONEXIONES_2521/2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CONECTO ENCHUFABLE CONSTRUCCION B6 HEMBRA HC-B 6-EBUS  PHOENIX CONTACT</t>
+          <t>LOTE DE MANGUERAS Y CONEXIONES_2521/2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -5589,13 +5587,13 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1771451</t>
+          <t>B6XX30IXXVMV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CONECTOR HC-B-10-KML-52/M1PG16MCA PHOENIX CONTACT</t>
+          <t>GUÍA DE DESGASTE PLANA CON UNIONES ENTRELAZADAS, DE .25" X 1.25" X 60"  DE UHMW CON SUJETADORES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -5608,7 +5606,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
@@ -5617,13 +5615,13 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1771723</t>
+          <t>BCC03WZ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SOPORTE DE CONTACTOS HEMBRAS HEAVY B24 PHOENIX CONTACT</t>
+          <t>Conector para Ethernet M12 D-coded , 4 polos</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -5645,13 +5643,13 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2281665</t>
+          <t>BDNTDTEAA01</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FLKM-D50 SUB/S/LA</t>
+          <t>T PARA DIVICE NET BDN T-DTE-AA-01</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
@@ -5664,7 +5662,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
@@ -5673,13 +5671,13 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1608740000</t>
+          <t>CA-D10X</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>END PLATE ZAP/TW 1</t>
+          <t xml:space="preserve">Conector para camara </t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -5692,7 +5690,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
@@ -5701,13 +5699,13 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1SFA616923R1118</t>
+          <t>CCS31-S8-M</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>FOCO PARA MODULO DE 5W A 115 VAC</t>
+          <t>SUJETADOR CABLE CLAMPS 5/16" COLOR NATURAL</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -5720,7 +5718,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
@@ -5729,13 +5727,13 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>258083</t>
+          <t>CDRA1BS100-180CZ</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
-          <t>RETEN PARA FLECHA HPV20-RB35-RF-01R -A</t>
+          <t xml:space="preserve">ACTUADOR NEUMATICO ROTATIVO DE 180° </t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5744,11 +5742,11 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
@@ -5757,13 +5755,13 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>090-ES009-00600</t>
+          <t xml:space="preserve">CINTA TEFLON </t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
-          <t>EMPAQUE FINAL SER. A Y J MILLER.....</t>
+          <t>CINTA TEFLON DE 1/2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -5776,7 +5774,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
@@ -5785,13 +5783,13 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2769585</t>
+          <t>CINTAS/AISLAR</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
-          <t>MCR-CP-I-I-00 AMPLIFICADOR</t>
+          <t>CINTA DE AISLAR</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -5804,7 +5802,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
@@ -5813,13 +5811,13 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2798682</t>
+          <t>CORTE_3180</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
-          <t>PROTECTOR PHOENIX CONTACT MODELO UAK 2-PE/S-X-120AC-ST</t>
+          <t>Corte láser de barrenos de 5 mm de diámetro en acero negro de 1/2 in</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5832,7 +5830,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
@@ -5841,13 +5839,13 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>S8LDA120</t>
+          <t>NS-01-27IGUS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
-          <t>BOBINA  PARKER S8LDA120</t>
+          <t>Slide</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5856,11 +5854,11 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>pza</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
@@ -5869,13 +5867,13 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>24-225-5</t>
+          <t>POLI.3MM</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
-          <t>IPS M5x25 FLAT HEAD SCREW No PARTE 24-225-5</t>
+          <t>POLICARBONATO SOLIDO 3.0MM 122X244 CRISTALINO</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -5888,7 +5886,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
@@ -5897,13 +5895,13 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FDR12H000000-02000</t>
+          <t>T1157L-G-120</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
-          <t>GUIA ORIGA DE 12MM X 2000MM</t>
+          <t>Lampara LED de 120 vac (solo led tipo bulbo) color verde</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -5912,11 +5910,11 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>MTS.</t>
+          <t>PZA</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
@@ -5925,13 +5923,13 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>P8S-EPFXS</t>
+          <t>TAPA CIEGA_22MM BOTONERA INDUSTRIALES</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SENSOR PNP PARA CILINDRO P1Q</t>
+          <t>TAPA CIEGA_22MM BOTONERA INDUSTRIALES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -5940,11 +5938,11 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
@@ -5953,13 +5951,13 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PK2002MA01</t>
+          <t>TRBU0805B-100</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK2002MA01)</t>
+          <t>MANGUERA ANTICHISPAS 8MM</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -5972,7 +5970,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
@@ -5981,13 +5979,13 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PK3202MA01</t>
+          <t>X3Z/S</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
-          <t>KIT D/SELLOS P/EMB P/CIL 2MA (PK3202MA01)</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -6000,7 +5998,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
@@ -6009,13 +6007,13 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>0801670</t>
+          <t>ZB4BVB1</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CES-SRG-BK</t>
+          <t>CUERPO PARA LAMPARA PILOTO</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -6037,13 +6035,13 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>0801675</t>
+          <t>ZB4BVB4</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
-          <t>CES-STPG-GY-5</t>
+          <t>BASE PARA LAMPARA PILOTO TELEMECANIC</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -6056,7 +6054,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
@@ -6065,13 +6063,13 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>0804155</t>
+          <t>ARBQ4000-00-P-1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
-          <t>EO-AB/UT/LED/15 Toma de corriente</t>
+          <t>INTERFACE REGULADOR</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -6084,7 +6082,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
@@ -6093,13 +6091,13 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>0827448</t>
+          <t>CABLE ETHERNET</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Soporte para señalización, negro, sin rotular, Tipo de montaje: Tornillos, remaches, Diámetro: 22 mm</t>
+          <t>CABLE ETHERNET CAT-6 UTP COLOR AZUL</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -6108,11 +6106,11 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>MTS.</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
@@ -6121,13 +6119,13 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>0913045</t>
+          <t>CAPUCHONRJ45</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
-          <t>FUSIBLE DE 10 AMPS.</t>
+          <t xml:space="preserve">BOTA PROTECTORA PARA CONCETOR RJ45 </t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -6140,7 +6138,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
@@ -6149,13 +6147,13 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>0921011</t>
+          <t>CINTILLA 5.5</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cabeza portafusible, corriente nominal: 6,3 A, longitud: 33,1 mm, anchura: 6,1 mm, altura: 45,7 mm, color: negro</t>
+          <t>CINTILLA 5.5</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -6168,7 +6166,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
@@ -6177,13 +6175,13 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2866381</t>
+          <t>CINTILLAS 3.5</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>TRIO-PS/1AC/24DC/20 Fuente aliment. carr. simétr., conmutada primario, monofásica, salida: 24 V DC / 20 A</t>
+          <t>CINTILLAS 3.5</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -6196,7 +6194,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
@@ -6205,13 +6203,13 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3204010</t>
+          <t>CINTILLAS 7.5</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>QT 1.5</t>
+          <t>CINTILLAS 7.5</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -6224,7 +6222,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>683</v>
       </c>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
@@ -6233,13 +6231,13 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1771338</t>
+          <t>MAQUINADOS_8045/1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CARC.EMPOT.C/BR.LONG.S/TAPA REF.HC-B 10AML</t>
+          <t>8045_POLEA CONVEYOR</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -6252,7 +6250,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
@@ -6261,13 +6259,13 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BESA12-CM</t>
+          <t>NFS-35</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Aditamento M12x1 "Cushioned Prox Mount"</t>
+          <t>CLUTCH (FRENO CONTRAVUELTA MARCA MORSE-REGAL)Model NFS 35 Standard Bore Size (In) 1.377.949,000 Standard Bore Size (mm) 35 Rated Torque Capacity (ft.-lbs.) 350 Rated Torque Capacity (N-M) 475</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -6280,7 +6278,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
@@ -6289,13 +6287,13 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ZBVB4</t>
+          <t>OP-51657</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>LUZ ROJA</t>
+          <t>CABLE E/S</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -6317,13 +6315,13 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>P3TFA98WEAN</t>
+          <t>PG16</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SEPARADOR DE LIQUIDOS 1 PULGADA</t>
+          <t>GLANDULA PG16 O DE 1" CON CONTRA TUERCA</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -6336,7 +6334,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
@@ -6345,13 +6343,13 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PR4506Q</t>
+          <t>REST.CARTUCHO</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ELEMENTO FILTRANTE</t>
+          <t>Resistencia tipo cartucho, 3/8" Diametro, 15 cm de longitud , 685w a 120w</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -6364,7 +6362,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
@@ -6373,13 +6371,13 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SWC30M30GZ</t>
+          <t>SAN1000-B</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ELEMENTO FILTRANTE</t>
+          <t>Silenciadores de 1/8bronce san1000-B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -6392,7 +6390,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
@@ -6401,13 +6399,13 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>_00221844</t>
+          <t>T1157L-B-120</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>EV 2/2</t>
+          <t>Lampara LED de 120 vac (solo led tipo bulbo) color azul</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6420,7 +6418,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
@@ -6429,13 +6427,13 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>_00783579</t>
+          <t>T1157L-B-24</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CONECTOR</t>
+          <t>LED 24 VDC AZUL</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -6448,7 +6446,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
@@ -6457,13 +6455,13 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1706010000</t>
+          <t>T1157L-Y-120</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CLEMA ZDU 2.5-2/3AN</t>
+          <t>Lampara LED de 120 vac (solo led tipo bulbo) color amarillo</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -6476,7 +6474,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
@@ -6485,13 +6483,13 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>0859170006</t>
+          <t>T1157L-Y-24</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CABLE PARA SENSOR..</t>
+          <t>LED 24 VDC AMARILLO</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -6504,7 +6502,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
@@ -6513,13 +6511,13 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BCS00LM</t>
+          <t>TEY340</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
-          <t>BCS M18BBG2-PSC15H-S04K</t>
+          <t>INTERRUPTOR CAJA MOLDEADORA 3P 40A 480V</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -6532,7 +6530,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
@@ -6541,13 +6539,13 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>BES0086</t>
+          <t>U-LHFR0.75</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SENSOR INDUCTIVO M18</t>
+          <t xml:space="preserve">BALERO LINEAL DE 3/4 CON HOUSING </t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -6556,11 +6554,11 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
@@ -6569,13 +6567,13 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BES22BS1</t>
+          <t>VPL-A0633F-PJ12AA</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Accesorio de mantaje para  sensor</t>
+          <t xml:space="preserve">SERVOMOTOR KINETIX VP DE BAJA INERCIA 240VAC , 4500 RPM , ENCODER  MULTI-VUELTAS , NO FRENO MCA ALLEN BRADLEY </t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -6584,7 +6582,7 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I219" t="n">
@@ -6597,13 +6595,13 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>P1D-B100MCE1300NGNNN</t>
+          <t>WS14X835</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CILINDRO NEUMATICO SERIE P1D 100mm BORE X1300mm STROKE MONTAJE TRUNION PUERTO NPTF</t>
+          <t>BOLSA ASPIRADORA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -6616,7 +6614,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
@@ -6625,13 +6623,13 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3SB34000C</t>
+          <t>MPL-B420P-MK72AA</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>BLOQUE DE CONTACTOS NC CON TERMINAL DE TORNILLO</t>
+          <t>MPL-B420P-MK72AA . SERVOMOTOR MPL , 460VCA , 5000 RPM ENCODER</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -6640,11 +6638,11 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
@@ -6653,13 +6651,13 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>62001J</t>
+          <t>OSPP500000004000000000</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>PORTAFUSIBLE DE 1 POLO PARA FUSIBLE TIPO J (62001J)</t>
+          <t>Actuador neumatico de cama, Embolo 50mm, carrera 400mm</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -6668,7 +6666,7 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>PIEZA</t>
         </is>
       </c>
       <c r="I222" t="n">
@@ -6681,13 +6679,13 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>6ES7972-0BB12-0XA0</t>
+          <t>ZBVB3</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CONECTOR PROFIBUS</t>
+          <t>LUZ VERDE</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -6709,13 +6707,13 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1608860000</t>
+          <t>KL9510</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TERMINAL BLOCK JUMPER, 2WAY, 5.1MM</t>
+          <t>Adaptador par bases para sensor P8S incluye 10 KL3333</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -6728,7 +6726,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
@@ -6737,13 +6735,13 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2701815</t>
+          <t xml:space="preserve">OSPL250300000850E00000000 </t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>AXIOLINE F , ACOPLADOR DE BUS , PROFINET , HEMBRA RJ45  , VELOCIDAD DE TRANSMISION EN EL BUS LOCAL : 100MBIT/S INDICE DE PROTECCION : IP20 , INCLUIDOS MODULO BASE DE BUS Y CONECTOR AXIOLINE F</t>
+          <t>RODLESS CYLINDER ORIGA</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -6752,11 +6750,11 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
-          <t>PIEZA</t>
+          <t>PZA</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
@@ -6765,13 +6763,13 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2958325</t>
+          <t>216537216598216600…//</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
-          <t>UM-ULA-400AC</t>
+          <t>BOTONERA COMPLETA DE DOS BOTONES , EN COLOR AMARILLO Y AZUL</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -6793,13 +6791,13 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BCC06M4</t>
+          <t>LKEH-202FV-RG</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
-          <t>BCC M434-0000-2A-000-41X475-000</t>
+          <t xml:space="preserve">LKEH-202FV-RG  ALARMA CONVINADA CON TORRE DE SEÑAL </t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -6821,13 +6819,13 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BES02KJ</t>
+          <t>THW18I-R</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SENSOR INDUCTIVO MARCA BALLUFF MODELO BES M18ML PSC50A S04G W</t>
+          <t>CABLE THW CAL 18 INDIANA ROJO</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -6836,11 +6834,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
-          <t>PZA</t>
+          <t>METROS</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
@@ -6849,3100 +6847,20 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>932679Q</t>
+          <t>Fecha de Impresión: 11 de noviembre de 2025 08:51</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Elemento de repuesto para filtro en línea de alta presión serie 50P</t>
-        </is>
-      </c>
+      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I229" t="n">
-        <v>1</v>
-      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>3RV1011-1CA15</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr"/>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>INTERRUPTOR AUTOM. TAM. S00, PARA PROTECC. MOTOR, CLASE 10, DISP.A 1,8...2,5A</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I230" t="n">
-        <v>2</v>
-      </c>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>5SL6104-7CC</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>INTERRUPTOR TERMOMAGNETICO 1P 4A P/RIEL 6KA 230/44VAC 60VDC0</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I231" t="n">
-        <v>1</v>
-      </c>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>5SL6316-7CC</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr"/>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>SIEMENS INTERRUPTOR TERMOMAG 3P 16A P/RIEL 6KA 230/44VAC 60VDC0</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I232" t="n">
-        <v>1</v>
-      </c>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>622-000-095</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr"/>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>LXR-0000-046</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I233" t="n">
-        <v>31</v>
-      </c>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>486265C4</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr"/>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>BOBINA 48 VCD POTENCIA 14 W</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I234" t="n">
-        <v>4</v>
-      </c>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>6GK1905-0FB00</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>SIEMENS MODELO 6GK1905-0FB00</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I235" t="n">
-        <v>4</v>
-      </c>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>750003//</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Mypnoz Screw terminals 3 polos sets 17.5.mm x1,x2,x3,x4</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I236" t="n">
-        <v>1</v>
-      </c>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>GLANDULA METALICA 1/2</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>GLANDULA METALICA DE 1/2</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I237" t="n">
-        <v>47</v>
-      </c>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>HTS-PA-12</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>INDICADOR HTS-PA-12 IGUS 12MM</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I238" t="n">
-        <v>2</v>
-      </c>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>INST.1197</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>SUMINISTTRO E INSTALACION DE 45 M DE TUBERIA DE CONDUIT DE 1/2 Y 150 M DE CABLE PARA LA ALIMENTACION ELECTRICA A INTERRUPTOR DE 30 AMP EN EL AREA DE SCRAP EN PLANTA CLARIOS</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I239" t="n">
-        <v>1</v>
-      </c>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>KQ2H08-10</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>CONECTOR RECTO DE 8MM MANG. A 10 MAN</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I240" t="n">
-        <v>17</v>
-      </c>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>BAM00A2</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>MOUNTING CLAMP FOR TUBULAR SENSOR</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I241" t="n">
-        <v>2</v>
-      </c>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>1020100000</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Clema Paso Wdu4 26-10awg 35a Tornillo</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I242" t="n">
-        <v>62</v>
-      </c>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>773110</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr"/>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>PNOZ m0p base unit not expandable, PNOZmulti Classic, dispositivobase, no ampliable, 4 salidas por semiconductor seguras, 2 salidas de relé seguras; Marca Pilz</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I243" t="n">
-        <v>2</v>
-      </c>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>750002//</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr"/>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Juego de terminales PNOZ s Setscrew terminals 12,5mm por resorte  (2A999990,  2A999991, 2A999992, 2A999993)</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I244" t="n">
-        <v>14</v>
-      </c>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>E11419</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr"/>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Conector M12 para válvula tipo A</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I245" t="n">
-        <v>1</v>
-      </c>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>JZ-500 3C AWG20</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr"/>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>MULTICONDUCTOR 3HILOS CALIBRE 20</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>MTS.</t>
-        </is>
-      </c>
-      <c r="I246" t="n">
-        <v>5</v>
-      </c>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>KB07601</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED AZUL 24V </t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I247" t="n">
-        <v>4</v>
-      </c>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>6ES7390-1AE80-0AA0</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr"/>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>RAIL SIEMENS MODELO 6ES7390-1AE80-0AA0</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I248" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>3206034</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>D-QT 2.5 TAPA FINAL</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I249" t="n">
-        <v>50</v>
-      </c>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>BDNTPTEAA01</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>TEE DE 7/8 DE 4 POLOS BDN T-PTE-AA-01</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I250" t="n">
-        <v>4</v>
-      </c>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>BES02N3</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>BES M08EH1-NSC20B-S04G-S  Sensor inductivo Steel Fac</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I251" t="n">
-        <v>1</v>
-      </c>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>BES02ZE</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>BES M18MN-USU80B-S21G</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I252" t="n">
-        <v>1</v>
-      </c>
-      <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>BLES51PA5F00PK</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>BLES-51-PA-5-F00-PK</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I253" t="n">
-        <v>2</v>
-      </c>
-      <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>BOS00EL</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr"/>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>BLS 18KF-XX-1LT-L-02</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I254" t="n">
-        <v>1</v>
-      </c>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>0129521</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>M24 Delta Protekt Nord-Lock Bolt Securing Washer/Pair</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I255" t="n">
-        <v>16</v>
-      </c>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>BAM00CH</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr"/>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>BES120KB5F  BASE DE MONTAJE PARA SENSOR DE 12 MM</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I256" t="n">
-        <v>6</v>
-      </c>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>BCC06YA</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>CONECTOR PARA PUERTO ESTANDAR M12 HEMBRA</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I257" t="n">
-        <v>1</v>
-      </c>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
-      <c r="L257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>BCC07YH</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>CONECTOR MACHO 7/8 4 POLOS C05 CN-A4-13</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I258" t="n">
-        <v>16</v>
-      </c>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>BES516324E5CS49</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>SENSOR PNP NORMALMENTE ABIERTO MODELO BES516324E5CS49</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I259" t="n">
-        <v>1</v>
-      </c>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>ROACA06B16C010F</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>RECEPTACULO BALLUFF MODELO ROA-CA-06-B-16C-010F</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I260" t="n">
-        <v>2</v>
-      </c>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>100-KFC40</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>CONTACTOS AUXILIARES MODELO 100-KFC40</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I261" t="n">
-        <v>4</v>
-      </c>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>1061200000</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>TOPES PARA WDU</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I262" t="n">
-        <v>8</v>
-      </c>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>CCS31-S8-M</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>SUJETADOR CABLE CLAMPS 5/16" COLOR NATURAL</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I263" t="n">
-        <v>30</v>
-      </c>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-      <c r="L263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>CDRA1BS100-180CZ</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ACTUADOR NEUMATICO ROTATIVO DE 180° </t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I264" t="n">
-        <v>1</v>
-      </c>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-      <c r="L264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>CINTAS/AISLAR</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr"/>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>CINTA DE AISLAR</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I265" t="n">
-        <v>6</v>
-      </c>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>ARBQ4000-00-P-1</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>INTERFACE REGULADOR</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I266" t="n">
-        <v>1</v>
-      </c>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>CABLE ETHERNET</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>CABLE ETHERNET CAT-6 UTP COLOR AZUL</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>MTS.</t>
-        </is>
-      </c>
-      <c r="I267" t="n">
-        <v>217</v>
-      </c>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-      <c r="L267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>CAPUCHONRJ45</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr"/>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BOTA PROTECTORA PARA CONCETOR RJ45 </t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I268" t="n">
-        <v>7</v>
-      </c>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-      <c r="L268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>6GK1905-0FA00</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>SIEMENS MODELO 6GK1905-0FA00</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I269" t="n">
-        <v>4</v>
-      </c>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>T1157L-B-24</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>LED 24 VDC AZUL</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I270" t="n">
-        <v>22</v>
-      </c>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>F1-SU1Z UN</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>PEDAL METALICO SENCILLO DE ACCION RAPIDO CON PROTECCION 1NC</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I271" t="n">
-        <v>1</v>
-      </c>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>T1157L-G-120</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr"/>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Lampara LED de 120 vac (solo led tipo bulbo) color verde</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I272" t="n">
-        <v>1</v>
-      </c>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>TAPA CIEGA_22MM BOTONERA INDUSTRIALES</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr"/>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>TAPA CIEGA_22MM BOTONERA INDUSTRIALES</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I273" t="n">
-        <v>90</v>
-      </c>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-      <c r="L273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>ZB4BVB1</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>CUERPO PARA LAMPARA PILOTO</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I274" t="n">
-        <v>2</v>
-      </c>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>ZBVB3</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>LUZ VERDE</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I275" t="n">
-        <v>1</v>
-      </c>
-      <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
-      <c r="L275" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>SAN1000-B</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Silenciadores de 1/8bronce san1000-B</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I276" t="n">
-        <v>4</v>
-      </c>
-      <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
-      <c r="L276" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>GLANDULA 3/4</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>PLASTIC GLANDULA 3/4 PLASTICO</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I277" t="n">
-        <v>60</v>
-      </c>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>MPL-B420P-MK72AA</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr"/>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>MPL-B420P-MK72AA . SERVOMOTOR MPL , 460VCA , 5000 RPM ENCODER</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I278" t="n">
-        <v>1</v>
-      </c>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="L278" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>OP-51657</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr"/>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>CABLE E/S</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I279" t="n">
-        <v>1</v>
-      </c>
-      <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
-      <c r="L279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>1684247</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>CARCAZA DE ACOPLAMIENTO LIBRE CAPERUZA DE PLASTICO RECTA PANTALLADO</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I280" t="n">
-        <v>1</v>
-      </c>
-      <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
-      <c r="L280" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>CINTILLA 5.5</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>CINTILLA 5.5</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I281" t="n">
-        <v>200</v>
-      </c>
-      <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
-      <c r="L281" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>MAQUINADOS_8045/1</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr"/>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>8045_POLEA CONVEYOR</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I282" t="n">
-        <v>2</v>
-      </c>
-      <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
-      <c r="L282" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>CTHW18CM//ROJO</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr"/>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>CABLE FLEXANEL ROJO 18</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>MTS.</t>
-        </is>
-      </c>
-      <c r="I283" t="n">
-        <v>300</v>
-      </c>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>CUADRO ADH.3/4"</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr"/>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>CUADRO ADHERIBLE DE 3/4" IT CAO75</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>PZA.</t>
-        </is>
-      </c>
-      <c r="I284" t="n">
-        <v>2</v>
-      </c>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>10M9531</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr"/>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Terminal de Anillo, M3.5, 6, Serie SCOTCHLOK, 14 AWG, Polyolefin</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I285" t="n">
-        <v>19</v>
-      </c>
-      <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>NFS-35</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr"/>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>CLUTCH (FRENO CONTRAVUELTA MARCA MORSE-REGAL)Model NFS 35 Standard Bore Size (In) 1.377.949,000 Standard Bore Size (mm) 35 Rated Torque Capacity (ft.-lbs.) 350 Rated Torque Capacity (N-M) 475</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I286" t="n">
-        <v>5</v>
-      </c>
-      <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
-      <c r="L286" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>PG16</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr"/>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>GLANDULA PG16 O DE 1" CON CONTRA TUERCA</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I287" t="n">
-        <v>4</v>
-      </c>
-      <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
-      <c r="L287" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>OSPP500000004000000000</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr"/>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Actuador neumatico de cama, Embolo 50mm, carrera 400mm</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I288" t="n">
-        <v>2</v>
-      </c>
-      <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
-      <c r="L288" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>800FM-LF5</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr"/>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Boton pulsador amarillo co indicador de 22mm</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I289" t="n">
-        <v>1</v>
-      </c>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="L289" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>E11420</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr"/>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>CABLE DE CONEXION</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I290" t="n">
-        <v>4</v>
-      </c>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>E50S8-250-3-T-24</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr"/>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Encoder incremental , diam 50mm, flecha solida de 8mm, salida totem pole (NPN/PNP)  250 PPR, fases: A, B, Z, Alimentación: 12 a 24 VCC, con cable de 2 mts</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I291" t="n">
-        <v>1</v>
-      </c>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>FREIGHT COST / FLETE</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr"/>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>COST OF SHIPPING (COSTO DE ENVIO DE MATERIAL)</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I292" t="n">
-        <v>1</v>
-      </c>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>GLANDULA METALICA 3/4</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr"/>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>GLANDULA METALICA DE 3/4</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I293" t="n">
-        <v>45</v>
-      </c>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>KB07518</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr"/>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>LED 24V COLOR ROJO 12 LEDS</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I294" t="n">
-        <v>4</v>
-      </c>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>KB07519</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr"/>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LED 24V AMARILLO  </t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
-      <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I295" t="n">
-        <v>14</v>
-      </c>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>REST.CARTUCHO</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr"/>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Resistencia tipo cartucho, 3/8" Diametro, 15 cm de longitud , 685w a 120w</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I296" t="n">
-        <v>1</v>
-      </c>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>2523T74</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr"/>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>RUEDA PARA ESTRUCTURA DE ALIMENTADOR DE TAPAS</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I297" t="n">
-        <v>2</v>
-      </c>
-      <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
-      <c r="L297" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>26-420-8P</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr"/>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>IPS TRESPA GRIS 8MM HOJA</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I298" t="n">
-        <v>0.9999999999999999</v>
-      </c>
-      <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
-      <c r="L298" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>MAQUINADOS_3372</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr"/>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>TOLVA:</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I299" t="n">
-        <v>1</v>
-      </c>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>CINTILLA 11"</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr"/>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>CINTILLA 11"</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>MTS.</t>
-        </is>
-      </c>
-      <c r="I300" t="n">
-        <v>300</v>
-      </c>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>CINTILLAS 7.5</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr"/>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>CINTILLAS 7.5</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I301" t="n">
-        <v>883</v>
-      </c>
-      <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>VPL-A0633F-PJ12AA</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr"/>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SERVOMOTOR KINETIX VP DE BAJA INERCIA 240VAC , 4500 RPM , ENCODER  MULTI-VUELTAS , NO FRENO MCA ALLEN BRADLEY </t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I302" t="n">
-        <v>2</v>
-      </c>
-      <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>B6XX30IXXVMV</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr"/>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>GUÍA DE DESGASTE PLANA CON UNIONES ENTRELAZADAS, DE .25" X 1.25" X 60"  DE UHMW CON SUJETADORES</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I303" t="n">
-        <v>6</v>
-      </c>
-      <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>BDNTDTEAA01</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr"/>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>T PARA DIVICE NET BDN T-DTE-AA-01</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr"/>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I304" t="n">
-        <v>1</v>
-      </c>
-      <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
-      <c r="L304" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CINTA TEFLON </t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr"/>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>CINTA TEFLON DE 1/2</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I305" t="n">
-        <v>3</v>
-      </c>
-      <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
-      <c r="L305" t="inlineStr"/>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>GLANDULA DE 1/2</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr"/>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>GLANDULA DE PLASTICO DE 1/2"</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I306" t="n">
-        <v>34</v>
-      </c>
-      <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
-      <c r="L306" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>JZ-500 18C AWG18</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>JZ-500 18C AWG18</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>METROS</t>
-        </is>
-      </c>
-      <c r="I307" t="n">
-        <v>60</v>
-      </c>
-      <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KB07309      </t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>AD-T12, FOCO BA15D LED-120V-ROJO 12 LEDS 120 V</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I308" t="n">
-        <v>2</v>
-      </c>
-      <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
-      <c r="L308" t="inlineStr"/>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>D-A73</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr"/>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>SENSOR PARA CILINDRO SMC</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I309" t="n">
-        <v>1</v>
-      </c>
-      <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>KL9510</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr"/>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Adaptador par bases para sensor P8S incluye 10 KL3333</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I310" t="n">
-        <v>10</v>
-      </c>
-      <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr"/>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OSPL250300000850E00000000 </t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr"/>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>RODLESS CYLINDER ORIGA</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I311" t="n">
-        <v>1</v>
-      </c>
-      <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>THW18I-R</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr"/>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>CABLE THW CAL 18 INDIANA ROJO</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>METROS</t>
-        </is>
-      </c>
-      <c r="I312" t="n">
-        <v>100</v>
-      </c>
-      <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>POLI.3MM</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr"/>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>POLICARBONATO SOLIDO 3.0MM 122X244 CRISTALINO</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I313" t="n">
-        <v>1</v>
-      </c>
-      <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>1769-RTB40DIO</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr"/>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>CONECTOR DE CONEXION MODELO 1769-RTB40DIO</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I314" t="n">
-        <v>1</v>
-      </c>
-      <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>198-H2</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr"/>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>MECANISMO ROTATORIO DE OPERACION DE INTERRUPTOR</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I315" t="n">
-        <v>1</v>
-      </c>
-      <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>CORTE_3180</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr"/>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Corte láser de barrenos de 5 mm de diámetro en acero negro de 1/2 in</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I316" t="n">
-        <v>5</v>
-      </c>
-      <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>LKEH-202FV-RG</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr"/>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LKEH-202FV-RG  ALARMA CONVINADA CON TORRE DE SEÑAL </t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I317" t="n">
-        <v>2</v>
-      </c>
-      <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>800FM-F2</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr"/>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Boton pulsador de 22mm negro</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I318" t="n">
-        <v>1</v>
-      </c>
-      <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>800FM-SM22</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr"/>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Selector 2 posiciones  22mm</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I319" t="n">
-        <v>1</v>
-      </c>
-      <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>1207860</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr"/>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>DATA-TWIST  11 PELACABLES</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I320" t="n">
-        <v>1</v>
-      </c>
-      <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>800T-QA24R</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr"/>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>BOTON DE PARO</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I321" t="n">
-        <v>2</v>
-      </c>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>855E-24TL7</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr"/>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Control Tower Stack Light, 24V AC/DC, LED, Type: Steady, Clear</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I322" t="n">
-        <v>1</v>
-      </c>
-      <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>T1157L-B-120</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr"/>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Lampara LED de 120 vac (solo led tipo bulbo) color azul</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr"/>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I323" t="n">
-        <v>5</v>
-      </c>
-      <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>T1157L-Y-120</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr"/>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Lampara LED de 120 vac (solo led tipo bulbo) color amarillo</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I324" t="n">
-        <v>4</v>
-      </c>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>T1157L-Y-24</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr"/>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>LED 24 VDC AMARILLO</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I325" t="n">
-        <v>1</v>
-      </c>
-      <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>TEY340</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr"/>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>INTERRUPTOR CAJA MOLDEADORA 3P 40A 480V</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I326" t="n">
-        <v>1</v>
-      </c>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>U-LHFR0.75</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr"/>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BALERO LINEAL DE 3/4 CON HOUSING </t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>PIEZA</t>
-        </is>
-      </c>
-      <c r="I327" t="n">
-        <v>4</v>
-      </c>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>WS14X835</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr"/>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>BOLSA ASPIRADORA</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I328" t="n">
-        <v>1</v>
-      </c>
-      <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>8F6X-S</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr"/>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>DESTORCEDOR DE 1/2 NPT FLEER CAMPANA</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I329" t="n">
-        <v>3</v>
-      </c>
-      <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>BCC03WZ</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr"/>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Conector para Ethernet M12 D-coded , 4 polos</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I330" t="n">
-        <v>1</v>
-      </c>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>CA-D10X</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr"/>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conector para camara </t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I331" t="n">
-        <v>1</v>
-      </c>
-      <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>CTHW18CM//BCO</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr"/>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CABLE THW CAL. 18 C. MTY  BLANCO </t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>MTS.</t>
-        </is>
-      </c>
-      <c r="I332" t="n">
-        <v>200</v>
-      </c>
-      <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
-      <c r="L332" t="inlineStr"/>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>NS-01-27IGUS</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr"/>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Slide</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>pza</t>
-        </is>
-      </c>
-      <c r="I333" t="n">
-        <v>2</v>
-      </c>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
-      <c r="L333" t="inlineStr"/>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>800T-H2</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr"/>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>SELECTOR DE DOS POSICIONES</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I334" t="n">
-        <v>3</v>
-      </c>
-      <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
-      <c r="L334" t="inlineStr"/>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>TRBU0805B-100</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr"/>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>MANGUERA ANTICHISPAS 8MM</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I335" t="n">
-        <v>100</v>
-      </c>
-      <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>X3Z/S</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr"/>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Manifold</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I336" t="n">
-        <v>1</v>
-      </c>
-      <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>ZB4BVB4</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr"/>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>BASE PARA LAMPARA PILOTO TELEMECANIC</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I337" t="n">
-        <v>2</v>
-      </c>
-      <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>216537216598216600…//</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr"/>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>BOTONERA COMPLETA DE DOS BOTONES , EN COLOR AMARILLO Y AZUL</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>PZA</t>
-        </is>
-      </c>
-      <c r="I338" t="n">
-        <v>1</v>
-      </c>
-      <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Fecha de Impresión: 12 de agosto de 2025 17:29</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr"/>
-      <c r="C339" t="inlineStr"/>
-      <c r="D339" t="inlineStr"/>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t>Página 1 de 1</t>
         </is>
